--- a/Paper/Sensing/MobiCom.xlsx
+++ b/Paper/Sensing/MobiCom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\学习\MSU\25FALL\825\awesome-pai\Paper\Sensing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8D20D7-C7F3-49B8-ADA2-080AD76F2F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA9EAC9-9C09-4842-94D1-470C445920D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>Wireless Actuation for Soft Electronics-free Robots</t>
   </si>
@@ -612,7 +612,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>48</v>
@@ -621,9 +621,6 @@
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>

--- a/Paper/Sensing/MobiCom.xlsx
+++ b/Paper/Sensing/MobiCom.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\学习\MSU\25FALL\825\awesome-pai\Paper\Sensing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA9EAC9-9C09-4842-94D1-470C445920D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40DA22E-1358-4050-9D99-367C950C0BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2024" sheetId="1" r:id="rId1"/>
+    <sheet name="2023 Summer" sheetId="1" r:id="rId1"/>
+    <sheet name="2023 Winter" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>Wireless Actuation for Soft Electronics-free Robots</t>
   </si>
@@ -231,6 +232,74 @@
   </si>
   <si>
     <t>EM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MilliMobile: An Autonomous Battery-free Wireless Microrobot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无电池自主机器人，用射频给小型电容器充电。移动慢，但是很小。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antenna</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignQuery: A Natural User Interface and Search Engine for Sign Languages with Wearable Sensors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>惯性传感器识别手势来实现手语搜索引擎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sign-to-911: Enabling 911 Service for Sign Language Users on Assistive AR Glasses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>识别手势转语音打电话给911</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AR眼镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APG: Audioplethysmography for Cardiac Monitoring in Hearables</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用主动降噪耳机发射低强度超声探测信号，由于耳道的体积随着血管变形而有形变，心跳会调节超声回声，用耳机的麦克风接收回声可以监测心脏状态。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动降噪耳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taming Event Cameras with Bio-Inspired Architecture and Algorithm: A Case for Drone Obstacle Avoidance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无人机避障，两个系统：一种基于交叉结构的信号处理管道，用于快速事件过滤和障碍物检测；以及一种基于外侧膝状体的事件匹配算法，用于精确定位障碍物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stereo event cameras（无人机自己的摄像头和雷达时间分辨率低或视场有限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Practically Adopting Human Activity Recognition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给IMU的数据搞增强的，提升人体活动识别准确性和泛化能力。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -805,4 +874,141 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B660B9A-5E2F-4540-8B6B-FDB3867BD31D}">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="47.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="64.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="23" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="23" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Paper/Sensing/MobiCom.xlsx
+++ b/Paper/Sensing/MobiCom.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\学习\MSU\25FALL\825\awesome-pai\Paper\Sensing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40DA22E-1358-4050-9D99-367C950C0BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB070965-B653-4585-836F-647903793957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Summer" sheetId="1" r:id="rId1"/>
     <sheet name="2023 Winter" sheetId="2" r:id="rId2"/>
+    <sheet name="2024" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="190">
   <si>
     <t>Wireless Actuation for Soft Electronics-free Robots</t>
   </si>
@@ -300,6 +301,484 @@
   </si>
   <si>
     <t>给IMU的数据搞增强的，提升人体活动识别准确性和泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notes/application</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turbocharge Speech Understanding with Pilot Inference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加速边缘设备的语音理解能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delivers SOTA accuracy; it reduces the end-to-end latency by 2x and reduces the offloading needs by 2x.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以和现有的语音模型、管道和框架兼容，降低延迟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crowd Analytics with a Single mmWave Radar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mmWave Radar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单个毫米波雷达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出的数学解法提升了人群密度估计精度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学解法不适用的情况上了TCN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现人群规模分析，推断异常事件、瓶颈点及人群参与度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感觉是搞智慧城市、管理什么的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hydra: Exploiting Multi-Bounce Scattering for Beyond-Field-of-View mmWave Radar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用多重反弹在不事先了解环境的情况下感知视场之外的物体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单雷达，克服定位盲区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本质是定位，所以一下也没想到应用场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exploring Biomagnetism for Inclusive Vital Sign Monitoring: Modeling and Implementation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血液流动在外部磁场影响下磁耦合效应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精准且包容性地监测不同肤色移动用户的心率与呼吸频率</t>
+  </si>
+  <si>
+    <t>有专门的硬件设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效化解人体多样性对生命体征监测性能的影响</t>
+  </si>
+  <si>
+    <t>生命体征检测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exploring the Feasibility of Remote Cardiac Auscultation Using Earphones</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耳机变成听诊器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耳机，还需在PCB板实现一些功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将耳机的扬声器重新用作麦克风，并使用它来捕获患者耳道的微小 PCG 信号。可以使用不同类型的耳机有效地恢复心音图 （PCG） 信号。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果看起来挺好的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>细粒度心音（即 PCG 信号）这俩都放other了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MetaBioLiq: A Wearable Passive Metasurface Aided mmWave Sensing Platform for BioFluids</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体外部生物体液</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计了一个3D 聚乳酸 （PLA） 结构，从空气中捕获电场能量（不需电池），并将其隧道传输到汗液中。一旦共振效应发生，分析来自无线射频接收器的返回信号，以解耦共振。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需电池能源，被动感知，材料环保。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过体液来收集健康信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF-Egg: An RF Solution for Fine-Grained Multi-Target and Multi-Task Egg Incubation Sensing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感知鸡蛋的孵化状态，涉及鸡胚胎的生育能力、孵化状态和早期死亡率三个任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以同时检测多个目标，同时监测16个准确率在90%以上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RFID标签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>养殖业，智慧工厂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gastag: A Gas Sensing Paradigm using Graphene-based Tags</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>廉价的有毒有害气体浓度检测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵敏度高，便宜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RFID标签和气体敏感材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作范围只有8.5m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要监测环境气体质量的地方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost-Effective Soil Carbon Sensing with Wi-Fi and Optical Signals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测土壤碳含量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器学习方法，本质有点boring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF和光信号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智慧农场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeaScan: An Energy-Efficient Underwater Camera for Wireless 3D Color Imaging</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水下环境 3D 成像，三个超低功耗单色图像、配备了不同的滤光片（红色、绿色和蓝色）传感器来重建彩色图像。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功耗非常非常低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海洋气候变化、海鲜生产和科学发现的长期监测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摄像头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UWBeacon: Lighting up Centimeter-Level Underwater Positioning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过商用现成的 LED 和摄像头水下定位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高精度，10米内可以实现6 cm以下的平均定位误差和1.5°以下的方向误差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED 和摄像头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>距离还是有点短</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精度应该一般</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perceptual-Centric Image Super-Resolution using Heterogeneous Processors on Mobile Devices</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>algorithm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加速图像超分辨率情景下的神经网络计算速度，同时最大限度地减少AI加速器对图像质量的影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在图像质量相当的情况下，感知图像质量提高了2×，SR计算延迟降低了5.6×</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以作为一个sensing的中间技术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GazeTrak: Exploring Acoustic-based Eye Tracking on a Glass Frame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个扬声器和四个麦克风连接到眼镜的每一侧。这些声学传感器通过向眼球发射编码的听不见的声音并接收反射信号来捕捉眼球和周围区域的形成，推断视线位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要专门设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AR/VR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需要摄像头也可以实现注视位置追踪。实现了 3.6° 的精度，在不同会话中实现了 4.9°，刷新率为 83.3 Hz，功率特征为 287.9 mW。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Malicious Attacks against Multi-Sensor Fusion in Autonomous Driving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>challenge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一种攻击方式同时可以攻击激光雷达摄像头和雷达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoiréVision: A Generalized Moiré-based Mechanism for 6-DoF Motion Sensing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依托高频光栅作为视觉标记，助力提取精细特征点以实现超高精度运动感知。简单来说就是用摩尔纹做定位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决不了摩尔纹就利用，感觉idea本身还是很有意思的，精度也不错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polaris: Accurate, Vision-free Fiducials for Mobile Robots with Magnetic Constellation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>other 磁场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用一些磁标签做一个磁场用于机器人的位置和姿态估计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精度高功耗低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要专门的硬件，应用场景目前看来应该主要在一些特定的地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定场所（例如工厂等）中机器人的位置和姿态操控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁标签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rethinking Orientation Estimation with Smartphone-equipped Ultra-wideband Chips</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UWB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用智能手机嵌入的UWB模块做定位和姿态估计，结合陀螺仪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精度更高，保持低延迟和低能耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果好，novelty可能不是很足，不过效果好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bere: A Novel Video Recommender System for Virtual Reality Using Human Behavioral Signals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用观众在观看 VR 视频时的行为反应来推断他们的偏好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hydra: Accurate Multi-Modal Leaf Wetness Sensing with mm-Wave and Camera Fusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mmWave Radar and camera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测定叶子持续湿润时间，确定植物病害发展程度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高精度和鲁棒性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hornbill: A Portable, Touchless, and Battery-Free Electrochemical Bio-tag for Multi-pesticide Detection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一种无线、无电池的电化学生物标签，将NFC技术的优势与电化学生物传感器相结合，实现便携式、精确和非接触式的多种农药检测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>other 电化学标签和NFC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只对9种农药进行了实验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体积小，易用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demeter: Reliable Cross-soil LPWAN with Low-cost Signal Polarization Alignment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LPWAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要定制的 PCB 电路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将传感器的天线部署埋在土壤中进行土壤监测的同时能够实现地下跨土壤通信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常COTS都可以接收，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCB电路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EVLeSen: In-Vehicle Sensing with EV-Leaked Signal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在座椅上设计导电布标签，利用电动汽车泄漏的电磁信号，识别身体运动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要布置导电标签，相当于整个座椅是传感器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需要额外的信号源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动驾驶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导电标签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZEROECG: Zero-Sensation ECG Monitoring By Exploring RFID MOSFET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无线、无电池、轻量化电子皮肤标签，在活动期间连续跟踪用户的心电图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -834,7 +1313,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1011,4 +1490,511 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144DE344-A11E-4E69-86BE-7D9C041E8163}">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.4140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.9140625" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="70" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="70" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F24" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G30" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Paper/Sensing/MobiCom.xlsx
+++ b/Paper/Sensing/MobiCom.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\学习\MSU\25FALL\825\awesome-pai\Paper\Sensing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB070965-B653-4585-836F-647903793957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D95E28-78D8-4BA4-99F0-BA56A192C294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Summer" sheetId="1" r:id="rId1"/>
     <sheet name="2023 Winter" sheetId="2" r:id="rId2"/>
     <sheet name="2024" sheetId="4" r:id="rId3"/>
+    <sheet name="2025" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="228">
   <si>
     <t>Wireless Actuation for Soft Electronics-free Robots</t>
   </si>
@@ -779,6 +780,158 @@
   </si>
   <si>
     <t>无线、无电池、轻量化电子皮肤标签，在活动期间连续跟踪用户的心电图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIPS: Real-Time Perception Fusion for Infrastructure-Assisted Autonomous Driving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mask Does Not Matter: Anti-Spoofing Face Authentication using mmWave without On-site Registration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Estimating Soil Moisture using RF Signals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IoTree: A Battery-free Wearable System with Biocompatible Sensors for Continuous Tree Health Monitoring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SmartLens : Sensing Eye Activities Using Zero-power Contact Lens </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enabling Secure Touch-to-Access Device Pairing based on Human Body's Electrical Response</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U-Star: An Underwater Navigation System based on Passive 3D Optical Identification Tags</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合来自路边基础设施和车辆的激光雷达结果，以实时改善车辆的感知</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LiDAR&amp;vison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>achieve decimeter-level and real-time (up to 100ms) perception fusion between driving vehicles and roadside infrastructure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只是路边基础设施匹配的话似乎对这种fusion的应用不是很充分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LiDAR&amp;camera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动驾驶，先放EM/RF里了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">软件定义无线电和 Raspberry Pi </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无接触检测土壤湿度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农业，我感觉这一块应用可以到时候全部写在一起写一个小节，因为技术上没啥东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用毫米波雷达扫描的人脸信息对人脸认证进行欺骗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COTS毫米波雷达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以在戴着口罩的情况下也解锁人脸认证，所以可以算作一个安全问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>监测活树内的水分和养分水平，风能供电，无电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自制小装置，小电路板加小塑料风扇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我实在没看明白modality是啥，先放other了，反正应用场景还是清楚的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据最远只能到1.8公里以外的基站，需要一个基站接收处理数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐形眼镜里装很小的天线做传感器来监测眼动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专门处理隐形眼镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>算是一种可穿戴设备吧，比较无感</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作距离就一米出头，还需要一个标签来跟踪用户的头部运动抵消自干扰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>other，电信号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦克风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体对流经它的电信号产生独特的反应，不同的身体对信号产生不同的反应。设备内置麦克风将环境声音捕获为熵源，并将其转换为电信号，随后由人体处理和传输以进行设备配对</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我觉得既然真要触摸匹配那用指纹不就好了，安全性还高多了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心idea是现在为了减少设备配对过程中用户参与使用了访问，这个文章是提升这点的安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无源光学标签进行水下位置识别，并嵌入了丰富的位置和指导信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visible light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信息量比一般的标签大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有一个专门的算法做移动种水下去噪、相对定位和稳健的数据解析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水下光学识别标签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水下导航</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1997,4 +2150,272 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EA6624-8EEF-44A4-8105-61407D1A1AAA}">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.4140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.9140625" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="70" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="70" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="G30" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Paper/Sensing/MobiCom.xlsx
+++ b/Paper/Sensing/MobiCom.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\学习\MSU\25FALL\825\awesome-pai\Paper\Sensing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D95E28-78D8-4BA4-99F0-BA56A192C294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE004A9-BAB0-42A0-AC19-53EFD29C9271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Summer" sheetId="1" r:id="rId1"/>
     <sheet name="2023 Winter" sheetId="2" r:id="rId2"/>
     <sheet name="2024" sheetId="4" r:id="rId3"/>
-    <sheet name="2025" sheetId="5" r:id="rId4"/>
+    <sheet name="2022" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
